--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484351_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484351_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6807</v>
+        <v>7.6558</v>
       </c>
       <c r="E2" t="n">
-        <v>10.4059</v>
+        <v>10.1631</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.7252</v>
+        <v>-2.5073</v>
       </c>
       <c r="G2" t="n">
         <v>6.1735</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0555</v>
+        <v>-0.0805</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3523</v>
+        <v>0.1095</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4078</v>
+        <v>-0.1899</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4603</v>
+        <v>6.2991</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7141</v>
+        <v>3.4713</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7461</v>
+        <v>2.8278</v>
       </c>
       <c r="G3" t="n">
         <v>-2.2157</v>
@@ -688,13 +688,13 @@
         <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3559</v>
+        <v>1.1948</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.7506</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3625</v>
+        <v>0.4442</v>
       </c>
       <c r="V3" t="n">
         <v>6.148</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3333</v>
+        <v>4.3001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3623</v>
+        <v>3.0295</v>
       </c>
       <c r="F4" t="n">
-        <v>0.971</v>
+        <v>1.2706</v>
       </c>
       <c r="G4" t="n">
         <v>1.6368</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4523</v>
+        <v>0.5145</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5034</v>
+        <v>0.1638</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0511</v>
+        <v>0.3507</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3716</v>
+        <v>0.4243</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1436</v>
+        <v>-0.982</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5153</v>
+        <v>1.4063</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7164</v>
@@ -844,13 +844,13 @@
         <v>2.3441</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8573</v>
+        <v>0.91</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3798</v>
+        <v>0.5415</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4775</v>
+        <v>0.3686</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9414</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0213</v>
+        <v>-0.037</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8843</v>
+        <v>-0.6647</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9056</v>
+        <v>0.6277</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2473</v>
+        <v>0.4479</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2205</v>
+        <v>0.6102</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0268</v>
+        <v>-0.1623</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2518</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1433</v>
+        <v>1.0438</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1086</v>
+        <v>-0.4313</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4992</v>
+        <v>-0.1645</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3638</v>
+        <v>-0.4336</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1354</v>
+        <v>0.269</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3674</v>
+        <v>-1.5627</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.077</v>
+        <v>0.1011</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2312</v>
+        <v>0.2856</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1542</v>
+        <v>-0.1845</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0331</v>
+        <v>-0.216</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0509</v>
+        <v>0.7694</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3814</v>
+        <v>-0.2473</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.408</v>
+        <v>-0.2205</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0266</v>
+        <v>-0.0268</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7263</v>
+        <v>0.2518</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3505</v>
+        <v>0.1433</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3758</v>
+        <v>0.1086</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1077</v>
+        <v>-0.4992</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7585</v>
+        <v>-0.3638</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3492</v>
+        <v>-0.1354</v>
       </c>
       <c r="P7" t="n">
         <v>-0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>-1.3674</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5437</v>
+        <v>-0.1603</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1432</v>
+        <v>0.1301</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4005</v>
+        <v>-0.2904</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2471</v>
+        <v>-0.4605</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7658</v>
+        <v>-0.2663</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5187</v>
+        <v>-0.1942</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4479</v>
+        <v>-0.3814</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6102</v>
+        <v>-0.408</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1623</v>
+        <v>0.0266</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6124000000000001</v>
+        <v>1.7263</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0438</v>
+        <v>0.3505</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4313</v>
+        <v>1.3758</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1645</v>
+        <v>-2.1077</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4336</v>
+        <v>-0.7585</v>
       </c>
       <c r="O8" t="n">
-        <v>0.269</v>
+        <v>-1.3492</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.5627</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1089</v>
+        <v>0.1162</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1845</v>
+        <v>-0.0391</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2934</v>
+        <v>0.1554</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6806</v>
+        <v>-1.5637</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5671</v>
+        <v>-1.0416</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1135</v>
+        <v>-0.5221</v>
       </c>
       <c r="G9" t="n">
         <v>0.7707000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6384</v>
+        <v>-0.5214</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.652</v>
+        <v>-0.1265</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0136</v>
+        <v>-0.395</v>
       </c>
       <c r="V9" t="n">
         <v>-0.0549</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1161</v>
+        <v>-3.7366</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1818</v>
+        <v>-2.0202</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9343</v>
+        <v>-1.7164</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1497</v>
@@ -1234,13 +1234,13 @@
         <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7944</v>
+        <v>-1.4149</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.6252</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0076</v>
+        <v>-0.7897</v>
       </c>
       <c r="V10" t="n">
         <v>0.6093</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.454</v>
+        <v>-5.7241</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1846</v>
+        <v>-2.4274</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2694</v>
+        <v>-3.2967</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0157</v>
@@ -1312,13 +1312,13 @@
         <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6923</v>
+        <v>-0.9623</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0522</v>
+        <v>-0.295</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6401</v>
+        <v>-0.6673</v>
       </c>
       <c r="V11" t="n">
         <v>-2.16</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.336299999999999</v>
+        <v>6.941399999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>7.671100000000003</v>
+        <v>8.276299999999997</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3348</v>
+        <v>-1.3349</v>
       </c>
       <c r="G12" t="n">
         <v>1.3027</v>
@@ -1390,10 +1390,10 @@
         <v>14.6508</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9079</v>
+        <v>-0.3027999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2899999999999999</v>
+        <v>0.8953000000000002</v>
       </c>
       <c r="U12" t="n">
         <v>-1.1979</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9354</v>
+        <v>2.8872</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2804</v>
+        <v>2.8537</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.345</v>
+        <v>0.0336</v>
       </c>
       <c r="G13" t="n">
         <v>0.1797</v>
@@ -1468,13 +1468,13 @@
         <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>4.0567</v>
+        <v>2.0085</v>
       </c>
       <c r="T13" t="n">
-        <v>3.9924</v>
+        <v>1.5657</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0643</v>
+        <v>0.4429</v>
       </c>
       <c r="V13" t="n">
         <v>1.285</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4824</v>
+        <v>2.7504</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1819</v>
+        <v>0.8897</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3005</v>
+        <v>1.8607</v>
       </c>
       <c r="G14" t="n">
         <v>1.023</v>
@@ -1546,13 +1546,13 @@
         <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0024</v>
+        <v>1.2704</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5364</v>
+        <v>0.1715</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5387</v>
+        <v>1.0989</v>
       </c>
       <c r="V14" t="n">
         <v>0.0664</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3268</v>
+        <v>1.975</v>
       </c>
       <c r="E15" t="n">
         <v>3.3789</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0521</v>
+        <v>-1.4039</v>
       </c>
       <c r="G15" t="n">
         <v>0.6434</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4529</v>
+        <v>0.1953</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1732</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2797</v>
+        <v>0.3686</v>
       </c>
       <c r="V15" t="n">
         <v>2.5037</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4542</v>
+        <v>0.4078</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1999</v>
+        <v>-0.391</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7457</v>
+        <v>0.7988</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0496</v>
@@ -1702,13 +1702,13 @@
         <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4865</v>
+        <v>0.3756</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6657</v>
+        <v>0.1432</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1793</v>
+        <v>0.2324</v>
       </c>
       <c r="V16" t="n">
         <v>0.2772</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3536</v>
+        <v>-0.52</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.432</v>
+        <v>-0.3178</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0784</v>
+        <v>-0.2022</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1209</v>
+        <v>1.0589</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4298</v>
+        <v>3.1901</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5507</v>
+        <v>-2.1313</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2849</v>
+        <v>1.8234</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3454</v>
+        <v>3.6838</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6303</v>
+        <v>-1.8604</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1639</v>
+        <v>-0.7645</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0844</v>
+        <v>-0.4937</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0795</v>
+        <v>-0.2708</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9118000000000001</v>
+        <v>0.5929</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.1638</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.125</v>
+        <v>0.4291</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.7578</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-1.3283</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4294</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6459</v>
+        <v>-0.6186</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9358</v>
+        <v>-1.1287</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7102000000000001</v>
+        <v>0.5101</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3824</v>
+        <v>1.1209</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1686</v>
+        <v>-0.4298</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2138</v>
+        <v>1.5507</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6332</v>
+        <v>2.2849</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0409</v>
+        <v>-0.3454</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6741</v>
+        <v>2.6303</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7492</v>
+        <v>-1.1639</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2095</v>
+        <v>-0.0844</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5397</v>
+        <v>-1.0795</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4589</v>
+        <v>-0.1768</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3026</v>
+        <v>-0.4835</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1563</v>
+        <v>0.3067</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9002</v>
+        <v>-1.3569</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4525</v>
+        <v>-0.8347</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3527</v>
+        <v>-0.5222</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6073</v>
+        <v>-1.3824</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2026</v>
+        <v>-0.1686</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4047</v>
+        <v>-1.2138</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6536</v>
+        <v>-0.6332</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6536</v>
+        <v>0.0409</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.6741</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9536</v>
+        <v>-0.7492</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.549</v>
+        <v>-0.2095</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4047</v>
+        <v>-0.5397</v>
       </c>
       <c r="P19" t="n">
         <v>0.1953</v>
@@ -1936,28 +1936,28 @@
         <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0076</v>
+        <v>-0.1699</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1061</v>
+        <v>-0.2015</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0985</v>
+        <v>0.0316</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0744</v>
+        <v>-1.4644</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3502</v>
+        <v>-2.7525</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4246</v>
+        <v>1.2882</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8062</v>
+        <v>-1.7461</v>
       </c>
       <c r="H20" t="n">
-        <v>1.163</v>
+        <v>-1.8803</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9692</v>
+        <v>0.1342</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4277</v>
+        <v>-1.1912</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7217</v>
+        <v>-2.0006</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2939</v>
+        <v>0.8093</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.234</v>
+        <v>-0.5548</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5587</v>
+        <v>0.1203</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6753</v>
+        <v>-0.6751</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4347</v>
+        <v>-0.5778</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6219</v>
+        <v>-0.5846</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1872</v>
+        <v>0.0068</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0936</v>
+        <v>0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.3708</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2617</v>
+        <v>-1.6686</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9548</v>
+        <v>0.3502</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6931</v>
+        <v>-2.0188</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7461</v>
+        <v>-0.8062</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8803</v>
+        <v>1.163</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1342</v>
+        <v>-1.9692</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1912</v>
+        <v>0.4277</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0006</v>
+        <v>1.7217</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8093</v>
+        <v>-1.2939</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5548</v>
+        <v>-1.234</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1203</v>
+        <v>-0.5587</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6751</v>
+        <v>-0.6753</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3751</v>
+        <v>0.8405</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.6219</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5883</v>
+        <v>0.2186</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6642</v>
+        <v>-2.0936</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6642</v>
+        <v>-2.3708</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4803</v>
+        <v>-2.4187</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.329</v>
+        <v>-0.2553</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1513</v>
+        <v>-2.1634</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0589</v>
+        <v>-1.6073</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1901</v>
+        <v>-1.2026</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1313</v>
+        <v>-0.4047</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8234</v>
+        <v>-0.6536</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6838</v>
+        <v>-0.6536</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.8604</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7645</v>
+        <v>-0.9536</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4937</v>
+        <v>-0.549</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2708</v>
+        <v>-0.4047</v>
       </c>
       <c r="P22" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3674</v>
+        <v>0.4891</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.3983</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5201</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.7578</v>
+        <v>-1.4959</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4294</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9104</v>
+        <v>-2.939</v>
       </c>
       <c r="E23" t="n">
         <v>-0.4575</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4529</v>
+        <v>-2.4815</v>
       </c>
       <c r="G23" t="n">
         <v>0.2631</v>
@@ -2248,13 +2248,13 @@
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5409</v>
+        <v>-0.5695</v>
       </c>
       <c r="T23" t="n">
         <v>-0.4237</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1173</v>
+        <v>-0.1459</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4373</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3361</v>
+        <v>-2.9658</v>
       </c>
       <c r="E24" t="n">
-        <v>1.334899999999999</v>
+        <v>1.334999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.671099999999999</v>
+        <v>-4.3006</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3026</v>
@@ -2326,13 +2326,13 @@
         <v>12.6972</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9079000000000003</v>
+        <v>4.278300000000001</v>
       </c>
       <c r="T24" t="n">
         <v>1.1979</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2901000000000001</v>
+        <v>3.0805</v>
       </c>
       <c r="V24" t="n">
         <v>-3.9881</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484351_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484351_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,31 +736,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3001</v>
+        <v>2.1652</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0295</v>
+        <v>0.8946</v>
       </c>
       <c r="F4" t="n">
         <v>1.2706</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6368</v>
+        <v>-0.4982</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8944</v>
+        <v>-0.0266</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7423999999999999</v>
+        <v>-0.4716</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8657</v>
+        <v>0.7308</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0438</v>
+        <v>0.1228</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8219</v>
+        <v>0.608</v>
       </c>
       <c r="M4" t="n">
         <v>-1.2289</v>
@@ -782,12 +797,17 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4243</v>
+        <v>2.1349</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.982</v>
+        <v>2.1349</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4063</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7164</v>
+        <v>2.1349</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2689</v>
+        <v>0.921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5525</v>
+        <v>1.214</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3128</v>
+        <v>2.1349</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1845</v>
+        <v>0.921</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4972</v>
+        <v>1.214</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0291</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0844</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9447</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5415</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3686</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +902,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.037</v>
+        <v>1.214</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6647</v>
+        <v>1.214</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6277</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4479</v>
+        <v>1.214</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6102</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1623</v>
+        <v>1.214</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6124000000000001</v>
+        <v>1.214</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0438</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4313</v>
+        <v>1.214</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1645</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4336</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.5627</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1011</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1845</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -938,12 +963,17 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.216</v>
+        <v>0.607</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9854000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7694</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2473</v>
+        <v>0.607</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2205</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0268</v>
+        <v>0.607</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2518</v>
+        <v>0.607</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1433</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1086</v>
+        <v>0.607</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4992</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3638</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1354</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1603</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1301</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2904</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4605</v>
+        <v>-0.037</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2663</v>
+        <v>-0.6647</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1942</v>
+        <v>0.6277</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3814</v>
+        <v>0.4479</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.408</v>
+        <v>0.6102</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0266</v>
+        <v>-0.1623</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7263</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3505</v>
+        <v>1.0438</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3758</v>
+        <v>-0.4313</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1077</v>
+        <v>-0.1645</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7585</v>
+        <v>-0.4336</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3492</v>
+        <v>0.269</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-1.5627</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1162</v>
+        <v>0.1011</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0391</v>
+        <v>0.2856</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1554</v>
+        <v>-0.1845</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,12 +1129,17 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5637</v>
+        <v>-0.216</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0416</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5221</v>
+        <v>0.7694</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7707000000000001</v>
+        <v>-0.2473</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1734</v>
+        <v>-0.2205</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.0268</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6792</v>
+        <v>0.2518</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0041</v>
+        <v>0.1433</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6751</v>
+        <v>0.1086</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9085</v>
+        <v>-0.4992</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1775</v>
+        <v>-0.3638</v>
       </c>
       <c r="O9" t="n">
-        <v>0.269</v>
+        <v>-0.1354</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.5395</v>
+        <v>-1.3674</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5214</v>
+        <v>-0.1603</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1265</v>
+        <v>0.1301</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.395</v>
+        <v>-0.2904</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0549</v>
+        <v>0.3869</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7366</v>
+        <v>-0.4605</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0202</v>
+        <v>-0.2663</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7164</v>
+        <v>-0.1942</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1497</v>
+        <v>-0.3814</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0481</v>
+        <v>-0.408</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1978</v>
+        <v>0.0266</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6369</v>
+        <v>1.7263</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2906</v>
+        <v>0.3505</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9275</v>
+        <v>1.3758</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5127</v>
+        <v>-2.1077</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2425</v>
+        <v>-0.7585</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2702</v>
+        <v>-1.3492</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3674</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4149</v>
+        <v>0.1162</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6252</v>
+        <v>-0.0391</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7897</v>
+        <v>0.1554</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7241</v>
+        <v>-0.7896</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4274</v>
+        <v>-2.196</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2967</v>
+        <v>1.4063</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0157</v>
+        <v>-1.9303</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3523</v>
+        <v>-1.2689</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3366</v>
+        <v>-0.6615</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0423</v>
+        <v>-0.9012</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2446</v>
+        <v>-1.1845</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2023</v>
+        <v>0.2833</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9735</v>
+        <v>-1.0291</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1077</v>
+        <v>-0.0844</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1342</v>
+        <v>-0.9447</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3674</v>
+        <v>-1.1721</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9623</v>
+        <v>0.91</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.295</v>
+        <v>0.5415</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6673</v>
+        <v>0.3686</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.16</v>
+        <v>-0.9414</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,307 +1400,323 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.941399999999998</v>
+        <v>-1.5637</v>
       </c>
       <c r="E12" t="n">
-        <v>8.276299999999997</v>
+        <v>-1.0416</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3349</v>
+        <v>-0.5221</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3027</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7448</v>
+        <v>-0.1734</v>
       </c>
       <c r="I12" t="n">
-        <v>4.0475</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>11.9896</v>
+        <v>1.6792</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2157</v>
+        <v>1.0041</v>
       </c>
       <c r="L12" t="n">
-        <v>8.774199999999999</v>
+        <v>0.6751</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.687</v>
+        <v>-0.9085</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.9605</v>
+        <v>-1.1775</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.7266</v>
+        <v>0.269</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9536</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6973</v>
+        <v>-2.5395</v>
       </c>
       <c r="R12" t="n">
-        <v>14.6508</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3027999999999998</v>
+        <v>-0.5214</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8953000000000002</v>
+        <v>-0.1265</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1979</v>
+        <v>-0.395</v>
       </c>
       <c r="V12" t="n">
-        <v>3.9879</v>
+        <v>-0.0549</v>
       </c>
       <c r="W12" t="n">
-        <v>8.0885</v>
+        <v>-0.0549</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.1007</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8872</v>
+        <v>-4.3436</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8537</v>
+        <v>-2.6272</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0336</v>
+        <v>-1.7164</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1797</v>
+        <v>-2.7567</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5311</v>
+        <v>0.0481</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3514</v>
+        <v>-2.8048</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0228</v>
+        <v>-1.2439</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2944</v>
+        <v>1.2906</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7284</v>
+        <v>-2.5345</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8431</v>
+        <v>-1.5127</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7634</v>
+        <v>-1.2425</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0797</v>
+        <v>-0.2702</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-1.3674</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0085</v>
+        <v>-1.4149</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5657</v>
+        <v>-0.6252</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4429</v>
+        <v>-0.7897</v>
       </c>
       <c r="V13" t="n">
-        <v>1.285</v>
+        <v>0.6093</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0664</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7504</v>
+        <v>-5.7241</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8897</v>
+        <v>-2.4274</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8607</v>
+        <v>-3.2967</v>
       </c>
       <c r="G14" t="n">
-        <v>1.023</v>
+        <v>-2.0157</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2277</v>
+        <v>-2.3523</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7953</v>
+        <v>0.3366</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6717</v>
+        <v>-1.0423</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6613</v>
+        <v>-1.2446</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0105</v>
+        <v>0.2023</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6487</v>
+        <v>-0.9735</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4336</v>
+        <v>-1.1077</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2152</v>
+        <v>0.1342</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-1.3674</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2704</v>
+        <v>-0.9623</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1715</v>
+        <v>-0.295</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0989</v>
+        <v>-0.6673</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0664</v>
+        <v>-2.16</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0664</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.975</v>
+        <v>6.941500000000003</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3789</v>
+        <v>8.276299999999996</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4039</v>
+        <v>-1.3349</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6434</v>
+        <v>1.302699999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1973</v>
+        <v>-2.7448</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4461</v>
+        <v>4.047499999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8263</v>
+        <v>11.9896</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4912</v>
+        <v>3.2157</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3352</v>
+        <v>8.774400000000002</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.183</v>
+        <v>-10.687</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2939</v>
+        <v>-5.9605</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8891</v>
+        <v>-4.7266</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3674</v>
+        <v>1.9536</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-12.6973</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>14.6508</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1953</v>
+        <v>-0.3027999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1732</v>
+        <v>0.8953000000000002</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3686</v>
+        <v>-1.1979</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5037</v>
+        <v>3.9879</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6559</v>
+        <v>8.0885</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1522</v>
-      </c>
+        <v>-4.1007</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4078</v>
+        <v>2.8872</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.391</v>
+        <v>2.8537</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7988</v>
+        <v>0.0336</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0496</v>
+        <v>0.1797</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2648</v>
+        <v>0.5311</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2152</v>
+        <v>-0.3514</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1653</v>
+        <v>2.0228</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0844</v>
+        <v>1.2944</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0809</v>
+        <v>0.7284</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.215</v>
+        <v>-1.8431</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3492</v>
+        <v>-0.7634</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1342</v>
+        <v>-1.0797</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3756</v>
+        <v>2.0085</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1432</v>
+        <v>1.5657</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2324</v>
+        <v>0.4429</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2772</v>
+        <v>1.285</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.52</v>
+        <v>2.7504</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3178</v>
+        <v>0.8897</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2022</v>
+        <v>1.8607</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0589</v>
+        <v>1.023</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1901</v>
+        <v>0.2277</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1313</v>
+        <v>0.7953</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8234</v>
+        <v>2.6717</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6838</v>
+        <v>0.6613</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.8604</v>
+        <v>2.0105</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7645</v>
+        <v>-1.6487</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4937</v>
+        <v>-0.4336</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2708</v>
+        <v>-1.2152</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5929</v>
+        <v>1.2704</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1638</v>
+        <v>0.1715</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4291</v>
+        <v>1.0989</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.7578</v>
+        <v>0.0664</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4294</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6186</v>
+        <v>1.975</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1287</v>
+        <v>3.3789</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5101</v>
+        <v>-1.4039</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1209</v>
+        <v>0.6434</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4298</v>
+        <v>0.1973</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5507</v>
+        <v>0.4461</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2849</v>
+        <v>2.8263</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3454</v>
+        <v>0.4912</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6303</v>
+        <v>2.3352</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1639</v>
+        <v>-2.183</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0844</v>
+        <v>-0.2939</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0795</v>
+        <v>-1.8891</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5627</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1768</v>
+        <v>0.1953</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4835</v>
+        <v>-0.1732</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3067</v>
+        <v>0.3686</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.5037</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.6559</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1522</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3569</v>
+        <v>1.214</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8347</v>
+        <v>1.214</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5222</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3824</v>
+        <v>1.214</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1686</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2138</v>
+        <v>1.214</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6332</v>
+        <v>1.214</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0409</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6741</v>
+        <v>1.214</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7492</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2095</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5397</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1699</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2015</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0316</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4644</v>
+        <v>0.4078</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7525</v>
+        <v>-0.391</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2882</v>
+        <v>0.7988</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7461</v>
+        <v>-0.0496</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8803</v>
+        <v>-0.2648</v>
       </c>
       <c r="I20" t="n">
+        <v>0.2152</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.215</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.3492</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.1342</v>
       </c>
-      <c r="J20" t="n">
-        <v>-1.1912</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-2.0006</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.8093</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-0.5548</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.1203</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-0.6751</v>
-      </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5778</v>
+        <v>0.3756</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5846</v>
+        <v>0.1432</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0068</v>
+        <v>0.2324</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6686</v>
+        <v>-0.52</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3502</v>
+        <v>-0.3178</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0188</v>
+        <v>-0.2022</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8062</v>
+        <v>1.0589</v>
       </c>
       <c r="H21" t="n">
-        <v>1.163</v>
+        <v>3.1901</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9692</v>
+        <v>-2.1313</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4277</v>
+        <v>1.8234</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7217</v>
+        <v>3.6838</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2939</v>
+        <v>-1.8604</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.234</v>
+        <v>-0.7645</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5587</v>
+        <v>-0.4937</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6753</v>
+        <v>-0.2708</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8405</v>
+        <v>0.5929</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6219</v>
+        <v>0.1638</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2186</v>
+        <v>0.4291</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0936</v>
+        <v>-2.7578</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>-1.3283</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3708</v>
+        <v>-1.4294</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2226,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4187</v>
+        <v>-1.3569</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2553</v>
+        <v>-0.8347</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1634</v>
+        <v>-0.5222</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6073</v>
+        <v>-1.3824</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2026</v>
+        <v>-0.1686</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4047</v>
+        <v>-1.2138</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6536</v>
+        <v>-0.6332</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6536</v>
+        <v>0.0409</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.6741</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9536</v>
+        <v>-0.7492</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.549</v>
+        <v>-0.2095</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4047</v>
+        <v>-0.5397</v>
       </c>
       <c r="P22" t="n">
         <v>0.1953</v>
@@ -2170,28 +2271,33 @@
         <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4891</v>
+        <v>-0.1699</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3983</v>
+        <v>-0.2015</v>
       </c>
       <c r="U22" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0316</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.939</v>
+        <v>-1.4644</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4575</v>
+        <v>-2.7525</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4815</v>
+        <v>1.2882</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2631</v>
+        <v>-1.7461</v>
       </c>
       <c r="H23" t="n">
-        <v>1.382</v>
+        <v>-1.8803</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1188</v>
+        <v>0.1342</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9429</v>
+        <v>-1.1912</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9824000000000001</v>
+        <v>-2.0006</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0395</v>
+        <v>0.8093</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6797</v>
+        <v>-0.5548</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3996</v>
+        <v>0.1203</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0793</v>
+        <v>-0.6751</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5695</v>
+        <v>-0.5778</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4237</v>
+        <v>-0.5846</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1459</v>
+        <v>0.0068</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4373</v>
+        <v>0.6642</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4373</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,401 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9658</v>
+        <v>-1.6686</v>
       </c>
       <c r="E24" t="n">
-        <v>1.334999999999999</v>
+        <v>0.3502</v>
       </c>
       <c r="F24" t="n">
+        <v>-2.0188</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.8062</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.9692</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.7217</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.2939</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.234</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.5587</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.6753</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.8405</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.6219</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.2186</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-2.0936</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.3708</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P. CAMPANA SOLER</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.8325</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.3427</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5101</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.093</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.4298</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.0709</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.3454</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.4163</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.1639</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.0844</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.0795</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.1768</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.4835</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q. BARDES BADIA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.4187</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.2553</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.1634</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.6073</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.2026</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.4047</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.6536</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.6536</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.9536</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.549</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.4047</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.4891</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S. ROMEO FO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.939</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.4575</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-2.4815</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.382</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.1188</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9429</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.9824000000000001</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.0395</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.6797</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.0793</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.5695</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.4237</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1459</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484351_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.965700000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="F28" t="n">
         <v>-4.3006</v>
       </c>
-      <c r="G24" t="n">
-        <v>-1.3026</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G28" t="n">
+        <v>-1.3025</v>
+      </c>
+      <c r="H28" t="n">
         <v>2.7451</v>
       </c>
-      <c r="I24" t="n">
-        <v>-4.0477</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="I28" t="n">
+        <v>-4.0476</v>
+      </c>
+      <c r="J28" t="n">
         <v>10.687</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K28" t="n">
         <v>5.960500000000001</v>
       </c>
-      <c r="L24" t="n">
-        <v>4.7267</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="L28" t="n">
+        <v>4.726699999999999</v>
+      </c>
+      <c r="M28" t="n">
         <v>-11.9895</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N28" t="n">
         <v>-3.2155</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O28" t="n">
         <v>-8.7742</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P28" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q28" t="n">
         <v>-14.6505</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R28" t="n">
         <v>12.6972</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S28" t="n">
         <v>4.278300000000001</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T28" t="n">
         <v>1.1979</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U28" t="n">
         <v>3.0805</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V28" t="n">
         <v>-3.9881</v>
       </c>
-      <c r="W24" t="n">
-        <v>4.1006</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="W28" t="n">
+        <v>4.100599999999999</v>
+      </c>
+      <c r="X28" t="n">
         <v>-8.0886</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
